--- a/reference/about.xlsx
+++ b/reference/about.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView xWindow="120" yWindow="110" windowWidth="15120" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="БД" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="213">
   <si>
     <t>Описание</t>
   </si>
@@ -344,12 +344,6 @@
     <t>Причуды</t>
   </si>
   <si>
-    <t>Любовь</t>
-  </si>
-  <si>
-    <t>Развод</t>
-  </si>
-  <si>
     <t>Ребенок</t>
   </si>
   <si>
@@ -639,6 +633,27 @@
   </si>
   <si>
     <t>стоимость</t>
+  </si>
+  <si>
+    <t>rules</t>
+  </si>
+  <si>
+    <t>Текущий набор правил</t>
+  </si>
+  <si>
+    <t>Любовь / Развод</t>
+  </si>
+  <si>
+    <t>Выбор правил игры</t>
+  </si>
+  <si>
+    <t>Классические</t>
+  </si>
+  <si>
+    <t>Свобода полов</t>
+  </si>
+  <si>
+    <t>Согласно правилам в части любви, развода, детей</t>
   </si>
 </sst>
 </file>
@@ -912,7 +927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -963,70 +978,92 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1323,21 +1360,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D92"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>51</v>
@@ -1347,1087 +1384,1104 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="27" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="27" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="27" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="27" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="27" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="27" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="23" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="27" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="23" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="27" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="27" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="27" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="23" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="27" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:4" ht="15" thickBot="1">
+      <c r="A23" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="28" t="s">
+      <c r="B23" s="29"/>
+      <c r="C23" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="22" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="22" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="24"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="40"/>
+      <c r="B26" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="24"/>
-      <c r="B26" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="40"/>
+      <c r="B27" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1">
+      <c r="A28" s="41"/>
+      <c r="B28" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27" t="s">
+      <c r="C28" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="22" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="22" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="24"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="24"/>
-      <c r="B31" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" thickBot="1">
+      <c r="A33" s="41"/>
+      <c r="B33" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="24"/>
-      <c r="B32" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A33" s="26"/>
-      <c r="B33" s="27" t="s">
+      <c r="C33" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="22" t="s">
+      <c r="B34" s="20"/>
+      <c r="C34" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="22" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="24"/>
+      <c r="A35" s="40"/>
       <c r="B35" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="40"/>
+      <c r="B36" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="24"/>
-      <c r="B36" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="40"/>
+      <c r="B37" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" thickBot="1">
+      <c r="A38" s="41"/>
+      <c r="B38" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="24"/>
-      <c r="B37" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="25" t="s">
+      <c r="C38" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="40"/>
+      <c r="B40" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="40"/>
+      <c r="B41" s="30" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="24"/>
-      <c r="B40" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="24"/>
-      <c r="B41" s="33" t="s">
-        <v>184</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="40"/>
+      <c r="B42" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="40"/>
+      <c r="B43" s="30" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="24"/>
-      <c r="B42" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D42" s="35" t="s">
+      <c r="C43" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" thickBot="1">
+      <c r="A44" s="41"/>
+      <c r="B44" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="34" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="24"/>
-      <c r="B43" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A44" s="26"/>
-      <c r="B44" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>191</v>
-      </c>
-    </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="22" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="22" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="24"/>
+      <c r="A46" s="40"/>
       <c r="B46" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="25" t="s">
-        <v>177</v>
+      <c r="D46" s="23" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="24"/>
-      <c r="B47" s="33" t="s">
-        <v>184</v>
+      <c r="A47" s="40"/>
+      <c r="B47" s="30" t="s">
+        <v>182</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="40"/>
+      <c r="B48" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="40"/>
+      <c r="B49" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="24"/>
-      <c r="B48" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="35" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" s="40"/>
+      <c r="B50" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="24"/>
-      <c r="B49" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="35" t="s">
+    <row r="51" spans="1:4">
+      <c r="A51" s="40"/>
+      <c r="B51" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="24"/>
-      <c r="B50" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" s="35" t="s">
+    <row r="52" spans="1:4" ht="15" thickBot="1">
+      <c r="A52" s="41"/>
+      <c r="B52" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" s="20"/>
+      <c r="C53" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="40"/>
+      <c r="B54" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="40"/>
+      <c r="B55" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" thickBot="1">
+      <c r="A56" s="41"/>
+      <c r="B56" s="33" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="24"/>
-      <c r="B51" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="35" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A52" s="26"/>
-      <c r="B52" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="22" t="s">
+      <c r="C56" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="20"/>
+      <c r="C57" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="24"/>
-      <c r="B54" s="16" t="s">
+      <c r="D57" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="40"/>
+      <c r="B58" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="40"/>
+      <c r="B59" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="24"/>
-      <c r="B55" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D55" s="38" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A56" s="26"/>
-      <c r="B56" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="24"/>
-      <c r="B58" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="24"/>
-      <c r="B59" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D59" s="40" t="s">
-        <v>186</v>
+      <c r="D59" s="37" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="24"/>
+      <c r="A60" s="40"/>
       <c r="B60" s="16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D60" s="40" t="s">
-        <v>207</v>
+      <c r="D60" s="37" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="24"/>
-      <c r="B61" s="33" t="s">
+      <c r="A61" s="40"/>
+      <c r="B61" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="C61" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="35" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A62" s="26"/>
-      <c r="B62" s="36" t="s">
+    </row>
+    <row r="62" spans="1:4" ht="15" thickBot="1">
+      <c r="A62" s="41"/>
+      <c r="B62" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="C62" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="22" t="s">
+      <c r="B63" s="20"/>
+      <c r="C63" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="22" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="24"/>
+      <c r="A64" s="40"/>
       <c r="B64" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="40"/>
+      <c r="B65" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="24"/>
-      <c r="B65" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D65" s="40" t="s">
-        <v>186</v>
+      <c r="D65" s="37" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="24"/>
+      <c r="A66" s="40"/>
       <c r="B66" s="16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D66" s="40" t="s">
-        <v>207</v>
+      <c r="D66" s="37" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="24"/>
-      <c r="B67" s="33" t="s">
+      <c r="A67" s="40"/>
+      <c r="B67" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A68" s="26"/>
-      <c r="B68" s="36" t="s">
+    </row>
+    <row r="68" spans="1:4" ht="15" thickBot="1">
+      <c r="A68" s="41"/>
+      <c r="B68" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="C68" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="22" t="s">
+      <c r="B69" s="20"/>
+      <c r="C69" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="22" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="24"/>
+      <c r="A70" s="40"/>
       <c r="B70" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="40"/>
+      <c r="B71" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="24"/>
-      <c r="B71" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="26"/>
-      <c r="B72" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72" s="41" t="s">
-        <v>207</v>
+      <c r="D71" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" thickBot="1">
+      <c r="A72" s="41"/>
+      <c r="B72" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="38" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B73" s="21"/>
-      <c r="C73" s="22" t="s">
+      <c r="B73" s="20"/>
+      <c r="C73" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="24"/>
+      <c r="A74" s="40"/>
       <c r="B74" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="40"/>
+      <c r="B75" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="24"/>
-      <c r="B75" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C75" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A76" s="26"/>
-      <c r="B76" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C76" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D76" s="41" t="s">
-        <v>207</v>
+      <c r="D75" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" thickBot="1">
+      <c r="A76" s="41"/>
+      <c r="B76" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D76" s="38" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B77" s="21"/>
-      <c r="C77" s="22" t="s">
+      <c r="B77" s="20"/>
+      <c r="C77" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="24"/>
+      <c r="A78" s="40"/>
       <c r="B78" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="40"/>
+      <c r="B79" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="24"/>
-      <c r="B79" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D79" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A80" s="26"/>
-      <c r="B80" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D80" s="41" t="s">
-        <v>207</v>
+      <c r="D79" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" thickBot="1">
+      <c r="A80" s="41"/>
+      <c r="B80" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D80" s="38" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B81" s="21"/>
-      <c r="C81" s="22" t="s">
+      <c r="B81" s="20"/>
+      <c r="C81" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="24"/>
+      <c r="A82" s="40"/>
       <c r="B82" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="40"/>
+      <c r="B83" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="24"/>
-      <c r="B83" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C83" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D83" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A84" s="26"/>
-      <c r="B84" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C84" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" s="41" t="s">
-        <v>207</v>
+      <c r="D83" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" thickBot="1">
+      <c r="A84" s="41"/>
+      <c r="B84" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D84" s="38" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="20" t="s">
+      <c r="A85" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="21"/>
-      <c r="C85" s="22" t="s">
+      <c r="B85" s="20"/>
+      <c r="C85" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D85" s="23" t="s">
+      <c r="D85" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="24"/>
+      <c r="A86" s="40"/>
       <c r="B86" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="40"/>
+      <c r="B87" s="16" t="s">
         <v>176</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D86" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="24"/>
-      <c r="B87" s="16" t="s">
-        <v>178</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D87" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A88" s="26"/>
-      <c r="B88" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D88" s="41" t="s">
-        <v>207</v>
+      <c r="D87" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" thickBot="1">
+      <c r="A88" s="41"/>
+      <c r="B88" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="38" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B89" s="21"/>
-      <c r="C89" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D89" s="23" t="s">
+      <c r="B89" s="20"/>
+      <c r="C89" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="30" t="s">
+      <c r="A90" s="27" t="s">
         <v>37</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D90" s="25" t="s">
+      <c r="D90" s="23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A91" s="31" t="s">
+    <row r="91" spans="1:4">
+      <c r="A91" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B91" s="32"/>
-      <c r="C91" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D91" s="28" t="s">
+      <c r="B91" s="44"/>
+      <c r="C91" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D91" s="46" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15" thickBot="1">
+      <c r="A92" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="48"/>
+      <c r="C92" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D92" s="34" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A45:A52"/>
     <mergeCell ref="A53:A56"/>
     <mergeCell ref="A57:A62"/>
     <mergeCell ref="A63:A68"/>
@@ -2436,11 +2490,6 @@
     <mergeCell ref="A81:A84"/>
     <mergeCell ref="A77:A80"/>
     <mergeCell ref="A73:A76"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A45:A52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -2449,43 +2498,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30">
+    <row r="2" spans="1:6" ht="29">
       <c r="A2" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -2494,100 +2543,100 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>95</v>
+        <v>127</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="9" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="3" t="s">
-        <v>96</v>
+        <v>127</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="14" t="s">
+        <v>211</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="9" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>127</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B6" s="42"/>
       <c r="C6" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B7" s="42"/>
       <c r="C7" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B8" s="42"/>
       <c r="C8" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="42" t="s">
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -2596,654 +2645,680 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B10" s="42"/>
       <c r="C10" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>107</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>108</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B13" s="42"/>
       <c r="C13" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="42" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>102</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42" t="s">
         <v>99</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="3" t="s">
         <v>100</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42" t="s">
         <v>101</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="3" t="s">
         <v>94</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B31" s="42"/>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="29">
       <c r="A32" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B32" s="42"/>
       <c r="C32" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B33" s="42"/>
       <c r="C33" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B34" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B34" s="42"/>
       <c r="C34" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B35" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="4"/>
+      <c r="C35" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="9" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="4"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="14" t="s">
+        <v>96</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="9" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="4"/>
+      <c r="A37" s="5"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="B38" s="42"/>
+      <c r="C38" s="14" t="s">
+        <v>208</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="12" t="s">
-        <v>170</v>
+      <c r="F38" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B39" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="B39" s="42"/>
       <c r="C39" s="3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="60">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="29">
       <c r="A40" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="B40" s="42"/>
+      <c r="C40" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="12" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="B41" s="42"/>
+      <c r="C41" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="58">
       <c r="A42" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="30">
-      <c r="A43" s="6" t="s">
-        <v>130</v>
+      <c r="F42" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="12" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="45">
-      <c r="A44" s="6" t="s">
-        <v>130</v>
+        <v>88</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30">
+        <v>89</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="29">
       <c r="A45" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="29">
       <c r="A46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="30">
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="29">
       <c r="A47" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="13" t="s">
-        <v>154</v>
+        <v>131</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="29">
       <c r="A49" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="30">
+      <c r="F49" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30">
+      <c r="F50" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="43.5">
       <c r="A51" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="30">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="29">
       <c r="A52" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="29">
       <c r="A53" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="30">
+      <c r="F53" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="29">
       <c r="A54" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="29">
+      <c r="A55" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="29">
+      <c r="A56" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="13" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B35:B39"/>
+  <mergeCells count="10">
+    <mergeCell ref="B35:B41"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="C14:C30"/>
     <mergeCell ref="D22:D29"/>
@@ -3252,6 +3327,7 @@
     <mergeCell ref="B2:B8"/>
     <mergeCell ref="B9:B13"/>
     <mergeCell ref="B14:B34"/>
+    <mergeCell ref="C35:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
